--- a/BRIN 3219/Diciembre/BRIN3219-EXPENSAS-Diciembre.xlsx
+++ b/BRIN 3219/Diciembre/BRIN3219-EXPENSAS-Diciembre.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BRIN 3219\Diciembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\BRIN 3219\Diciembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED7BC959-16A2-4D73-BBA7-1435AB370117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8E4374-9B38-4A34-A525-2B3128563624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$N$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$106</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$103</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="167">
   <si>
     <t>U.F.</t>
   </si>
@@ -220,9 +220,6 @@
   </si>
   <si>
     <t>5.23</t>
-  </si>
-  <si>
-    <t>SALDO ACTUAL</t>
   </si>
   <si>
     <t>DEUDA</t>
@@ -483,24 +480,15 @@
     <t>subidos en n0v</t>
   </si>
   <si>
-    <t xml:space="preserve">Lema ascensores - Adelanto cambio de guiadores </t>
-  </si>
-  <si>
     <t xml:space="preserve">Ascensor </t>
   </si>
   <si>
-    <t>Ingreso por parte de UF 1.7 (700USD) para cubrir gastos proporcionales a su UF del arreglo del ascensor de la venta de esa UF -  Esta UF paga sus extraordinarias por adelantado</t>
-  </si>
-  <si>
     <t>La UF 1.7 tiene a favor este dinero para cubrir sus extraordinarias -  aquí llevaremos la cuenta de como se va descontando el mismo</t>
   </si>
   <si>
     <t>Ingreso 14/11</t>
   </si>
   <si>
-    <t>Desratizacion de emergencia - 28/11</t>
-  </si>
-  <si>
     <t>Reemplazo Sra. Monica</t>
   </si>
   <si>
@@ -550,6 +538,12 @@
   </si>
   <si>
     <t>Julio Doartero - Colocacion de canasto</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Lema ascensores - Pago parcial arreglo guiadores Resta abonar $1.481.119,5</t>
+  </si>
+  <si>
+    <t>INGRESO</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1352,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1651,16 +1645,93 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="2" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="21" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="30" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1679,18 +1750,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1709,9 +1768,6 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1721,81 +1777,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1820,6 +1801,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="30" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2266,17 +2248,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K111"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K108"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2291,23 +2273,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="193"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="195"/>
+      <c r="D2" s="216"/>
+      <c r="E2" s="217"/>
+      <c r="F2" s="217"/>
+      <c r="G2" s="217"/>
+      <c r="H2" s="218"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="208">
+      <c r="E3" s="226">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="208"/>
-      <c r="G3" s="208"/>
-      <c r="H3" s="209"/>
+      <c r="F3" s="226"/>
+      <c r="G3" s="226"/>
+      <c r="H3" s="227"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2315,7 +2297,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="55" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H4" s="11"/>
     </row>
@@ -2335,7 +2317,7 @@
         <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H6" s="11"/>
     </row>
@@ -2343,7 +2325,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2351,13 +2333,13 @@
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
       <c r="E8" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2386,14 +2368,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="205"/>
-      <c r="B12" s="206"/>
-      <c r="C12" s="206"/>
-      <c r="D12" s="206"/>
-      <c r="E12" s="206"/>
-      <c r="F12" s="206"/>
-      <c r="G12" s="206"/>
-      <c r="H12" s="207"/>
+      <c r="A12" s="224"/>
+      <c r="B12" s="187"/>
+      <c r="C12" s="187"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="225"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2405,21 +2387,21 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="214" t="s">
-        <v>125</v>
-      </c>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214"/>
-      <c r="F14" s="214"/>
-      <c r="G14" s="214"/>
-      <c r="H14" s="214"/>
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="198" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" s="198"/>
+      <c r="C14" s="198"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+      <c r="F14" s="198"/>
+      <c r="G14" s="198"/>
+      <c r="H14" s="198"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="176" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B15" s="139"/>
       <c r="C15" s="139"/>
@@ -2428,12 +2410,12 @@
       <c r="F15" s="139"/>
       <c r="G15" s="139"/>
       <c r="H15" s="73">
-        <v>333220</v>
+        <v>302625.5</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="176" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" s="139"/>
       <c r="C16" s="139"/>
@@ -2442,13 +2424,13 @@
       <c r="F16" s="139"/>
       <c r="G16" s="139"/>
       <c r="H16" s="73">
-        <v>-52482.15</v>
+        <v>-47663.53</v>
       </c>
       <c r="I16" s="7"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="176" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B17" s="139"/>
       <c r="C17" s="139"/>
@@ -2457,13 +2439,13 @@
       <c r="F17" s="139"/>
       <c r="G17" s="139"/>
       <c r="H17" s="73">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="176" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B18" s="139"/>
       <c r="C18" s="139"/>
@@ -2471,14 +2453,14 @@
       <c r="E18" s="139"/>
       <c r="F18" s="139"/>
       <c r="G18" s="139"/>
-      <c r="H18" s="188">
+      <c r="H18" s="73">
         <v>283132.11</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="176" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B19" s="139"/>
       <c r="C19" s="139"/>
@@ -2486,14 +2468,14 @@
       <c r="E19" s="139"/>
       <c r="F19" s="139"/>
       <c r="G19" s="139"/>
-      <c r="H19" s="188">
+      <c r="H19" s="73">
         <v>-44593.3</v>
       </c>
       <c r="I19" s="7"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="176" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B20" s="139"/>
       <c r="C20" s="139"/>
@@ -2501,14 +2483,14 @@
       <c r="E20" s="139"/>
       <c r="F20" s="139"/>
       <c r="G20" s="139"/>
-      <c r="H20" s="188">
+      <c r="H20" s="73">
         <v>0.19</v>
       </c>
       <c r="I20" s="7"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="176" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="139"/>
       <c r="C21" s="139"/>
@@ -2518,25 +2500,25 @@
       <c r="G21" s="139"/>
       <c r="H21" s="69">
         <f>SUM(H15:H20)</f>
-        <v>519277</v>
+        <v>493501.47</v>
       </c>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="201" t="s">
-        <v>144</v>
-      </c>
-      <c r="B22" s="201"/>
-      <c r="C22" s="201"/>
-      <c r="D22" s="201"/>
-      <c r="E22" s="201"/>
-      <c r="F22" s="201"/>
-      <c r="G22" s="201"/>
-      <c r="H22" s="201"/>
-    </row>
-    <row r="23" spans="1:9">
+    <row r="22" spans="1:9" ht="0.75" customHeight="1">
+      <c r="A22" s="220" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="220"/>
+      <c r="C22" s="220"/>
+      <c r="D22" s="220"/>
+      <c r="E22" s="220"/>
+      <c r="F22" s="220"/>
+      <c r="G22" s="220"/>
+      <c r="H22" s="220"/>
+    </row>
+    <row r="23" spans="1:9" hidden="1">
       <c r="A23" s="176" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B23" s="139"/>
       <c r="C23" s="139"/>
@@ -2544,13 +2526,11 @@
       <c r="E23" s="139"/>
       <c r="F23" s="139"/>
       <c r="G23" s="139"/>
-      <c r="H23" s="73">
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="H23" s="73"/>
+    </row>
+    <row r="24" spans="1:9" hidden="1">
       <c r="A24" s="176" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B24" s="139"/>
       <c r="C24" s="139"/>
@@ -2558,13 +2538,11 @@
       <c r="E24" s="139"/>
       <c r="F24" s="139"/>
       <c r="G24" s="139"/>
-      <c r="H24" s="73">
-        <v>4519.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="H24" s="73"/>
+    </row>
+    <row r="25" spans="1:9" hidden="1">
       <c r="A25" s="176" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" s="139"/>
       <c r="C25" s="139"/>
@@ -2574,24 +2552,24 @@
       <c r="G25" s="139"/>
       <c r="H25" s="69">
         <f>SUM(H23:H24)</f>
-        <v>54519.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="200" t="s">
-        <v>131</v>
-      </c>
-      <c r="B26" s="200"/>
-      <c r="C26" s="200"/>
-      <c r="D26" s="200"/>
-      <c r="E26" s="200"/>
-      <c r="F26" s="200"/>
-      <c r="G26" s="200"/>
-      <c r="H26" s="200"/>
+      <c r="A26" s="219" t="s">
+        <v>130</v>
+      </c>
+      <c r="B26" s="219"/>
+      <c r="C26" s="219"/>
+      <c r="D26" s="219"/>
+      <c r="E26" s="219"/>
+      <c r="F26" s="219"/>
+      <c r="G26" s="219"/>
+      <c r="H26" s="219"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B27" s="139"/>
       <c r="C27" s="139"/>
@@ -2599,7 +2577,7 @@
       <c r="E27" s="139"/>
       <c r="F27" s="139"/>
       <c r="G27" s="139"/>
-      <c r="H27" s="188">
+      <c r="H27" s="73">
         <v>32000</v>
       </c>
     </row>
@@ -2615,7 +2593,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="139" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B29" s="139"/>
       <c r="C29" s="139"/>
@@ -2629,16 +2607,16 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="14.25" customHeight="1">
-      <c r="A30" s="196" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="196"/>
-      <c r="C30" s="196"/>
-      <c r="D30" s="196"/>
-      <c r="E30" s="196"/>
-      <c r="F30" s="196"/>
-      <c r="G30" s="196"/>
-      <c r="H30" s="196"/>
+      <c r="A30" s="199" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="199"/>
+      <c r="C30" s="199"/>
+      <c r="D30" s="199"/>
+      <c r="E30" s="199"/>
+      <c r="F30" s="199"/>
+      <c r="G30" s="199"/>
+      <c r="H30" s="199"/>
     </row>
     <row r="31" spans="1:9" hidden="1">
       <c r="A31" s="176"/>
@@ -2652,7 +2630,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="176" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32" s="177"/>
       <c r="C32" s="139"/>
@@ -2660,14 +2638,14 @@
       <c r="E32" s="139"/>
       <c r="F32" s="139"/>
       <c r="G32" s="139"/>
-      <c r="H32" s="188">
+      <c r="H32" s="73">
         <f>34791.3+1666.1+14994.9</f>
         <v>51452.3</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="139" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B33" s="139"/>
       <c r="C33" s="139"/>
@@ -2681,7 +2659,7 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="139" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B34" s="139"/>
       <c r="C34" s="139"/>
@@ -2695,20 +2673,20 @@
       </c>
     </row>
     <row r="35" spans="1:8">
-      <c r="A35" s="196" t="s">
-        <v>132</v>
-      </c>
-      <c r="B35" s="196"/>
-      <c r="C35" s="196"/>
-      <c r="D35" s="196"/>
-      <c r="E35" s="196"/>
-      <c r="F35" s="196"/>
-      <c r="G35" s="196"/>
-      <c r="H35" s="196"/>
+      <c r="A35" s="199" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="199"/>
+      <c r="C35" s="199"/>
+      <c r="D35" s="199"/>
+      <c r="E35" s="199"/>
+      <c r="F35" s="199"/>
+      <c r="G35" s="199"/>
+      <c r="H35" s="199"/>
     </row>
     <row r="36" spans="1:8" ht="14.25" customHeight="1">
       <c r="A36" s="139" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B36" s="139"/>
       <c r="C36" s="139"/>
@@ -2716,13 +2694,13 @@
       <c r="E36" s="139"/>
       <c r="F36" s="139"/>
       <c r="G36" s="139"/>
-      <c r="H36" s="188">
+      <c r="H36" s="73">
         <v>759994.39</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="178" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B37" s="139"/>
       <c r="C37" s="139"/>
@@ -2730,13 +2708,13 @@
       <c r="E37" s="139"/>
       <c r="F37" s="139"/>
       <c r="G37" s="139"/>
-      <c r="H37" s="188">
+      <c r="H37" s="73">
         <v>83788.34</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="139" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B38" s="139"/>
       <c r="C38" s="139"/>
@@ -2750,20 +2728,20 @@
       </c>
     </row>
     <row r="39" spans="1:8">
-      <c r="A39" s="214" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="214"/>
-      <c r="C39" s="214"/>
-      <c r="D39" s="214"/>
-      <c r="E39" s="214"/>
-      <c r="F39" s="214"/>
-      <c r="G39" s="214"/>
-      <c r="H39" s="214"/>
+      <c r="A39" s="198" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="198"/>
+      <c r="C39" s="198"/>
+      <c r="D39" s="198"/>
+      <c r="E39" s="198"/>
+      <c r="F39" s="198"/>
+      <c r="G39" s="198"/>
+      <c r="H39" s="198"/>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="80" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B40" s="139"/>
       <c r="C40" s="139"/>
@@ -2771,13 +2749,13 @@
       <c r="E40" s="139"/>
       <c r="F40" s="139"/>
       <c r="G40" s="139"/>
-      <c r="H40" s="188">
+      <c r="H40" s="73">
         <v>85000</v>
       </c>
     </row>
     <row r="41" spans="1:8">
-      <c r="A41" s="189" t="s">
-        <v>69</v>
+      <c r="A41" s="80" t="s">
+        <v>165</v>
       </c>
       <c r="B41" s="139"/>
       <c r="C41" s="139"/>
@@ -2785,13 +2763,14 @@
       <c r="E41" s="139"/>
       <c r="F41" s="139"/>
       <c r="G41" s="139"/>
-      <c r="H41" s="188">
-        <v>4200000</v>
+      <c r="H41" s="73">
+        <f>1000000+712434.25</f>
+        <v>1712434.25</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="139" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B42" s="139"/>
       <c r="C42" s="139"/>
@@ -2799,13 +2778,13 @@
       <c r="E42" s="139"/>
       <c r="F42" s="139"/>
       <c r="G42" s="139"/>
-      <c r="H42" s="188">
+      <c r="H42" s="73">
         <v>21629.39</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="139" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B43" s="139"/>
       <c r="C43" s="139"/>
@@ -2813,13 +2792,13 @@
       <c r="E43" s="139"/>
       <c r="F43" s="139"/>
       <c r="G43" s="139"/>
-      <c r="H43" s="188">
+      <c r="H43" s="73">
         <v>60000</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="139" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B44" s="139"/>
       <c r="C44" s="139"/>
@@ -2827,13 +2806,13 @@
       <c r="E44" s="139"/>
       <c r="F44" s="139"/>
       <c r="G44" s="139"/>
-      <c r="H44" s="188">
+      <c r="H44" s="73">
         <v>65000</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="139" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B45" s="139"/>
       <c r="C45" s="139"/>
@@ -2841,13 +2820,13 @@
       <c r="E45" s="139"/>
       <c r="F45" s="139"/>
       <c r="G45" s="139"/>
-      <c r="H45" s="188">
+      <c r="H45" s="73">
         <v>135000</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="80" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B46" s="139"/>
       <c r="C46" s="139"/>
@@ -2855,13 +2834,13 @@
       <c r="E46" s="139"/>
       <c r="F46" s="139"/>
       <c r="G46" s="139"/>
-      <c r="H46" s="188">
+      <c r="H46" s="73">
         <v>350000</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="80" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B47" s="139"/>
       <c r="C47" s="139"/>
@@ -2869,13 +2848,13 @@
       <c r="E47" s="139"/>
       <c r="F47" s="139"/>
       <c r="G47" s="139"/>
-      <c r="H47" s="188">
+      <c r="H47" s="73">
         <v>350000</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="80" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B48" s="139"/>
       <c r="C48" s="139"/>
@@ -2883,13 +2862,13 @@
       <c r="E48" s="139"/>
       <c r="F48" s="139"/>
       <c r="G48" s="139"/>
-      <c r="H48" s="188">
+      <c r="H48" s="73">
         <v>35000</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="14.25" customHeight="1">
       <c r="A49" s="80" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="B49" s="139"/>
       <c r="C49" s="139"/>
@@ -2897,13 +2876,13 @@
       <c r="E49" s="139"/>
       <c r="F49" s="139"/>
       <c r="G49" s="139"/>
-      <c r="H49" s="188">
+      <c r="H49" s="73">
         <v>30000</v>
       </c>
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="139" t="s">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="B50" s="139"/>
       <c r="C50" s="139"/>
@@ -2911,41 +2890,43 @@
       <c r="E50" s="139"/>
       <c r="F50" s="139"/>
       <c r="G50" s="139"/>
-      <c r="H50" s="73">
-        <v>200000</v>
-      </c>
-      <c r="J50" s="6"/>
+      <c r="H50" s="69">
+        <f>SUM(H40:H49)</f>
+        <v>2844063.6399999997</v>
+      </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="139" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="139"/>
-      <c r="C51" s="139"/>
-      <c r="D51" s="139"/>
-      <c r="E51" s="139"/>
-      <c r="F51" s="139"/>
-      <c r="G51" s="139"/>
-      <c r="H51" s="69">
-        <f>SUM(H40:H50)</f>
-        <v>5531629.3899999997</v>
-      </c>
+      <c r="A51" s="198" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" s="198"/>
+      <c r="C51" s="198"/>
+      <c r="D51" s="198"/>
+      <c r="E51" s="198"/>
+      <c r="F51" s="198"/>
+      <c r="G51" s="198"/>
+      <c r="H51" s="198"/>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="214" t="s">
-        <v>134</v>
-      </c>
-      <c r="B52" s="214"/>
-      <c r="C52" s="214"/>
-      <c r="D52" s="214"/>
-      <c r="E52" s="214"/>
-      <c r="F52" s="214"/>
-      <c r="G52" s="214"/>
-      <c r="H52" s="214"/>
+      <c r="A52" s="139" t="s">
+        <v>70</v>
+      </c>
+      <c r="B52" s="139"/>
+      <c r="C52" s="139"/>
+      <c r="D52" s="139"/>
+      <c r="E52" s="139"/>
+      <c r="F52" s="139"/>
+      <c r="G52" s="139"/>
+      <c r="H52" s="73">
+        <v>170100</v>
+      </c>
+      <c r="J52" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="139" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="B53" s="139"/>
       <c r="C53" s="139"/>
@@ -2954,67 +2935,65 @@
       <c r="F53" s="139"/>
       <c r="G53" s="139"/>
       <c r="H53" s="73">
-        <v>170100</v>
-      </c>
-      <c r="J53" t="s">
-        <v>145</v>
+        <v>35000</v>
       </c>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="139" t="s">
-        <v>118</v>
-      </c>
+      <c r="A54" s="139"/>
       <c r="B54" s="139"/>
       <c r="C54" s="139"/>
       <c r="D54" s="139"/>
       <c r="E54" s="139"/>
       <c r="F54" s="139"/>
       <c r="G54" s="139"/>
-      <c r="H54" s="73">
-        <v>35000</v>
-      </c>
+      <c r="H54" s="73"/>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="139"/>
+      <c r="A55" s="139" t="s">
+        <v>73</v>
+      </c>
       <c r="B55" s="139"/>
       <c r="C55" s="139"/>
       <c r="D55" s="139"/>
       <c r="E55" s="139"/>
       <c r="F55" s="139"/>
       <c r="G55" s="139"/>
-      <c r="H55" s="73"/>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" s="139" t="s">
-        <v>74</v>
-      </c>
-      <c r="B56" s="139"/>
-      <c r="C56" s="139"/>
-      <c r="D56" s="139"/>
-      <c r="E56" s="139"/>
-      <c r="F56" s="139"/>
-      <c r="G56" s="139"/>
-      <c r="H56" s="179">
-        <f>SUM(H53:H55)</f>
+      <c r="H55" s="179">
+        <f>SUM(H52:H54)</f>
         <v>205100</v>
       </c>
-      <c r="K56" s="7"/>
+      <c r="K55" s="7"/>
+    </row>
+    <row r="56" spans="1:11" s="6" customFormat="1">
+      <c r="A56" s="200" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="201"/>
+      <c r="C56" s="201"/>
+      <c r="D56" s="201"/>
+      <c r="E56" s="201"/>
+      <c r="F56" s="201"/>
+      <c r="G56" s="201"/>
+      <c r="H56" s="202"/>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="215" t="s">
-        <v>135</v>
-      </c>
-      <c r="B57" s="216"/>
-      <c r="C57" s="216"/>
-      <c r="D57" s="216"/>
-      <c r="E57" s="216"/>
-      <c r="F57" s="216"/>
-      <c r="G57" s="216"/>
-      <c r="H57" s="217"/>
+      <c r="A57" s="80" t="s">
+        <v>119</v>
+      </c>
+      <c r="B57" s="80"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="80"/>
+      <c r="E57" s="80"/>
+      <c r="F57" s="80"/>
+      <c r="G57" s="80"/>
+      <c r="H57" s="73">
+        <v>24990</v>
+      </c>
+      <c r="I57" s="60"/>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
       <c r="A58" s="80" t="s">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="B58" s="80"/>
       <c r="C58" s="80"/>
@@ -3022,37 +3001,32 @@
       <c r="E58" s="80"/>
       <c r="F58" s="80"/>
       <c r="G58" s="80"/>
-      <c r="H58" s="188">
+      <c r="H58" s="69">
+        <f>SUM(H57)</f>
         <v>24990</v>
       </c>
-      <c r="I58" s="60"/>
     </row>
     <row r="59" spans="1:11" s="6" customFormat="1">
-      <c r="A59" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="B59" s="80"/>
-      <c r="C59" s="80"/>
-      <c r="D59" s="80"/>
-      <c r="E59" s="80"/>
-      <c r="F59" s="80"/>
-      <c r="G59" s="80"/>
-      <c r="H59" s="69">
-        <f>SUM(H58)</f>
-        <v>24990</v>
-      </c>
+      <c r="A59" s="198" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" s="198"/>
+      <c r="C59" s="198"/>
+      <c r="D59" s="198"/>
+      <c r="E59" s="198"/>
+      <c r="F59" s="198"/>
+      <c r="G59" s="198"/>
+      <c r="H59" s="198"/>
     </row>
     <row r="60" spans="1:11" s="6" customFormat="1">
-      <c r="A60" s="214" t="s">
-        <v>136</v>
-      </c>
-      <c r="B60" s="214"/>
-      <c r="C60" s="214"/>
-      <c r="D60" s="214"/>
-      <c r="E60" s="214"/>
-      <c r="F60" s="214"/>
-      <c r="G60" s="214"/>
-      <c r="H60" s="214"/>
+      <c r="A60" s="80"/>
+      <c r="B60" s="80"/>
+      <c r="C60" s="80"/>
+      <c r="D60" s="80"/>
+      <c r="E60" s="80"/>
+      <c r="F60" s="80"/>
+      <c r="G60" s="80"/>
+      <c r="H60" s="73"/>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1">
       <c r="A61" s="80"/>
@@ -3065,295 +3039,296 @@
       <c r="H61" s="73"/>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1">
-      <c r="A62" s="80"/>
-      <c r="B62" s="80"/>
-      <c r="C62" s="80"/>
-      <c r="D62" s="80"/>
-      <c r="E62" s="80"/>
-      <c r="F62" s="80"/>
-      <c r="G62" s="80"/>
-      <c r="H62" s="73"/>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1">
-      <c r="A63" s="175"/>
-      <c r="B63" s="175"/>
-      <c r="C63" s="175"/>
-      <c r="D63" s="175"/>
-      <c r="E63" s="175"/>
-      <c r="F63" s="175"/>
-      <c r="G63" s="175"/>
-      <c r="H63" s="174">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
-      <c r="A64" s="80" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="80"/>
-      <c r="D64" s="80"/>
-      <c r="E64" s="80"/>
-      <c r="F64" s="80"/>
-      <c r="G64" s="80"/>
-      <c r="H64" s="69">
-        <f>SUM(H61:H63)</f>
-        <v>0</v>
-      </c>
-      <c r="I64" s="60"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A65" s="215"/>
-      <c r="B65" s="216"/>
-      <c r="C65" s="216"/>
-      <c r="D65" s="216"/>
-      <c r="E65" s="216"/>
-      <c r="F65" s="216"/>
-      <c r="G65" s="216"/>
-      <c r="H65" s="217"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A66" s="81"/>
-      <c r="B66" s="82"/>
-      <c r="C66" s="82"/>
-      <c r="D66" s="82"/>
-      <c r="E66" s="82"/>
-      <c r="F66" s="82"/>
-      <c r="G66" s="82"/>
-      <c r="H66" s="158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A67" s="159"/>
-      <c r="B67" s="160"/>
-      <c r="C67" s="160"/>
-      <c r="D67" s="160"/>
-      <c r="E67" s="160"/>
-      <c r="F67" s="160"/>
-      <c r="G67" s="160"/>
-      <c r="H67" s="161">
+      <c r="A62" s="175"/>
+      <c r="B62" s="175"/>
+      <c r="C62" s="175"/>
+      <c r="D62" s="175"/>
+      <c r="E62" s="175"/>
+      <c r="F62" s="175"/>
+      <c r="G62" s="175"/>
+      <c r="H62" s="174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="21" customHeight="1">
+      <c r="A63" s="80" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="80"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="80"/>
+      <c r="E63" s="80"/>
+      <c r="F63" s="80"/>
+      <c r="G63" s="80"/>
+      <c r="H63" s="69">
+        <f>SUM(H60:H62)</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="60"/>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="200"/>
+      <c r="B64" s="201"/>
+      <c r="C64" s="201"/>
+      <c r="D64" s="201"/>
+      <c r="E64" s="201"/>
+      <c r="F64" s="201"/>
+      <c r="G64" s="201"/>
+      <c r="H64" s="202"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A65" s="81"/>
+      <c r="B65" s="82"/>
+      <c r="C65" s="82"/>
+      <c r="D65" s="82"/>
+      <c r="E65" s="82"/>
+      <c r="F65" s="82"/>
+      <c r="G65" s="82"/>
+      <c r="H65" s="158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A66" s="159"/>
+      <c r="B66" s="160"/>
+      <c r="C66" s="160"/>
+      <c r="D66" s="160"/>
+      <c r="E66" s="160"/>
+      <c r="F66" s="160"/>
+      <c r="G66" s="160"/>
+      <c r="H66" s="161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A67" s="162"/>
+      <c r="B67" s="163"/>
+      <c r="C67" s="163"/>
+      <c r="D67" s="163"/>
+      <c r="E67" s="163"/>
+      <c r="F67" s="163"/>
+      <c r="G67" s="163"/>
+      <c r="H67" s="158">
+        <f>H65+H66</f>
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A68" s="162"/>
-      <c r="B68" s="163"/>
-      <c r="C68" s="163"/>
-      <c r="D68" s="163"/>
-      <c r="E68" s="163"/>
-      <c r="F68" s="163"/>
-      <c r="G68" s="163"/>
-      <c r="H68" s="158">
-        <f>H66+H67</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A69" s="223" t="s">
+      <c r="A68" s="211" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="212"/>
+      <c r="C68" s="212"/>
+      <c r="D68" s="212"/>
+      <c r="E68" s="212"/>
+      <c r="F68" s="212"/>
+      <c r="G68" s="212"/>
+      <c r="H68" s="164">
+        <f>H63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A69" s="214"/>
+      <c r="B69" s="214"/>
+      <c r="C69" s="214"/>
+      <c r="D69" s="214"/>
+      <c r="E69" s="214"/>
+      <c r="F69" s="214"/>
+      <c r="G69" s="214"/>
+      <c r="H69" s="214"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A70" s="215"/>
+      <c r="B70" s="215"/>
+      <c r="C70" s="215"/>
+      <c r="D70" s="215"/>
+      <c r="E70" s="215"/>
+      <c r="F70" s="215"/>
+      <c r="G70" s="215"/>
+      <c r="H70" s="215"/>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A71" s="213" t="s">
+        <v>83</v>
+      </c>
+      <c r="B71" s="213"/>
+      <c r="C71" s="213"/>
+      <c r="D71" s="213"/>
+      <c r="E71" s="213"/>
+      <c r="F71" s="213"/>
+      <c r="G71" s="213"/>
+      <c r="H71" s="165"/>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A72" s="221"/>
+      <c r="B72" s="222"/>
+      <c r="C72" s="222"/>
+      <c r="D72" s="222"/>
+      <c r="E72" s="222"/>
+      <c r="F72" s="222"/>
+      <c r="G72" s="223"/>
+      <c r="H72" s="73"/>
+    </row>
+    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A73" s="129" t="s">
+        <v>74</v>
+      </c>
+      <c r="B73" s="80"/>
+      <c r="C73" s="80"/>
+      <c r="D73" s="80"/>
+      <c r="E73" s="80"/>
+      <c r="F73" s="80"/>
+      <c r="G73" s="80"/>
+      <c r="H73" s="69">
+        <f>SUM(H72:H72)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A74" s="130"/>
+      <c r="B74" s="130"/>
+      <c r="C74" s="130"/>
+      <c r="D74" s="130"/>
+      <c r="E74" s="130"/>
+      <c r="F74" s="130"/>
+      <c r="G74" s="130"/>
+      <c r="H74" s="131"/>
+    </row>
+    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A75" s="194" t="s">
         <v>82</v>
       </c>
-      <c r="B69" s="224"/>
-      <c r="C69" s="224"/>
-      <c r="D69" s="224"/>
-      <c r="E69" s="224"/>
-      <c r="F69" s="224"/>
-      <c r="G69" s="224"/>
-      <c r="H69" s="164">
-        <f>H64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A70" s="191"/>
-      <c r="B70" s="191"/>
-      <c r="C70" s="191"/>
-      <c r="D70" s="191"/>
-      <c r="E70" s="191"/>
-      <c r="F70" s="191"/>
-      <c r="G70" s="191"/>
-      <c r="H70" s="191"/>
-    </row>
-    <row r="71" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A71" s="192"/>
-      <c r="B71" s="192"/>
-      <c r="C71" s="192"/>
-      <c r="D71" s="192"/>
-      <c r="E71" s="192"/>
-      <c r="F71" s="192"/>
-      <c r="G71" s="192"/>
-      <c r="H71" s="192"/>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A72" s="190" t="s">
+      <c r="B75" s="195"/>
+      <c r="C75" s="195"/>
+      <c r="D75" s="195"/>
+      <c r="E75" s="195"/>
+      <c r="F75" s="195"/>
+      <c r="G75" s="195"/>
+      <c r="H75" s="132">
+        <f>H73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A76" s="206" t="s">
+        <v>88</v>
+      </c>
+      <c r="B76" s="207"/>
+      <c r="C76" s="207"/>
+      <c r="D76" s="207"/>
+      <c r="E76" s="207"/>
+      <c r="F76" s="207"/>
+      <c r="G76" s="208"/>
+      <c r="H76" s="132"/>
+    </row>
+    <row r="77" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A77" s="206" t="s">
+        <v>93</v>
+      </c>
+      <c r="B77" s="207"/>
+      <c r="C77" s="207"/>
+      <c r="D77" s="207"/>
+      <c r="E77" s="207"/>
+      <c r="F77" s="207"/>
+      <c r="G77" s="208"/>
+      <c r="H77" s="132"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75">
+      <c r="A78" s="194" t="s">
+        <v>89</v>
+      </c>
+      <c r="B78" s="195"/>
+      <c r="C78" s="195"/>
+      <c r="D78" s="195"/>
+      <c r="E78" s="195"/>
+      <c r="F78" s="195"/>
+      <c r="G78" s="195"/>
+      <c r="H78" s="132">
+        <f>H29+H38+H50+H55+H58+H34+H21+H25</f>
+        <v>4494890.1399999997</v>
+      </c>
+      <c r="J78" s="173"/>
+      <c r="K78" s="144"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75">
+      <c r="A79" s="203" t="s">
+        <v>122</v>
+      </c>
+      <c r="B79" s="204"/>
+      <c r="C79" s="204"/>
+      <c r="D79" s="204"/>
+      <c r="E79" s="204"/>
+      <c r="F79" s="204"/>
+      <c r="G79" s="205"/>
+      <c r="H79" s="133">
+        <f>H76+H78</f>
+        <v>4494890.1399999997</v>
+      </c>
+      <c r="I79" s="128"/>
+      <c r="J79" s="186"/>
+      <c r="K79" s="186"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75">
+      <c r="A80" s="203" t="s">
+        <v>94</v>
+      </c>
+      <c r="B80" s="204"/>
+      <c r="C80" s="204"/>
+      <c r="D80" s="204"/>
+      <c r="E80" s="204"/>
+      <c r="F80" s="204"/>
+      <c r="G80" s="205"/>
+      <c r="H80" s="134">
+        <f>H77+H75</f>
+        <v>0</v>
+      </c>
+      <c r="J80" s="144"/>
+    </row>
+    <row r="81" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A81" s="209" t="s">
         <v>84</v>
       </c>
-      <c r="B72" s="190"/>
-      <c r="C72" s="190"/>
-      <c r="D72" s="190"/>
-      <c r="E72" s="190"/>
-      <c r="F72" s="190"/>
-      <c r="G72" s="190"/>
-      <c r="H72" s="165"/>
-    </row>
-    <row r="73" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A73" s="202"/>
-      <c r="B73" s="203"/>
-      <c r="C73" s="203"/>
-      <c r="D73" s="203"/>
-      <c r="E73" s="203"/>
-      <c r="F73" s="203"/>
-      <c r="G73" s="204"/>
-      <c r="H73" s="73"/>
-    </row>
-    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A74" s="129" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74" s="80"/>
-      <c r="C74" s="80"/>
-      <c r="D74" s="80"/>
-      <c r="E74" s="80"/>
-      <c r="F74" s="80"/>
-      <c r="G74" s="80"/>
-      <c r="H74" s="69">
-        <f>SUM(H73:H73)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A75" s="130"/>
-      <c r="B75" s="130"/>
-      <c r="C75" s="130"/>
-      <c r="D75" s="130"/>
-      <c r="E75" s="130"/>
-      <c r="F75" s="130"/>
-      <c r="G75" s="130"/>
-      <c r="H75" s="131"/>
-    </row>
-    <row r="76" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A76" s="210" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" s="211"/>
-      <c r="C76" s="211"/>
-      <c r="D76" s="211"/>
-      <c r="E76" s="211"/>
-      <c r="F76" s="211"/>
-      <c r="G76" s="211"/>
-      <c r="H76" s="132">
-        <f>H74</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A77" s="197" t="s">
-        <v>89</v>
-      </c>
-      <c r="B77" s="198"/>
-      <c r="C77" s="198"/>
-      <c r="D77" s="198"/>
-      <c r="E77" s="198"/>
-      <c r="F77" s="198"/>
-      <c r="G77" s="199"/>
-      <c r="H77" s="132"/>
-    </row>
-    <row r="78" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A78" s="197" t="s">
-        <v>94</v>
-      </c>
-      <c r="B78" s="198"/>
-      <c r="C78" s="198"/>
-      <c r="D78" s="198"/>
-      <c r="E78" s="198"/>
-      <c r="F78" s="198"/>
-      <c r="G78" s="199"/>
-      <c r="H78" s="132"/>
-    </row>
-    <row r="79" spans="1:11" ht="18">
-      <c r="A79" s="210" t="s">
-        <v>90</v>
-      </c>
-      <c r="B79" s="211"/>
-      <c r="C79" s="211"/>
-      <c r="D79" s="211"/>
-      <c r="E79" s="211"/>
-      <c r="F79" s="211"/>
-      <c r="G79" s="211"/>
-      <c r="H79" s="132">
-        <f>H29+H38+H51+H56+H59+H34+H21+H25</f>
-        <v>7262751.169999999</v>
-      </c>
-      <c r="J79" s="173"/>
-      <c r="K79" s="144"/>
-    </row>
-    <row r="80" spans="1:11" ht="18">
-      <c r="A80" s="218" t="s">
-        <v>123</v>
-      </c>
-      <c r="B80" s="219"/>
-      <c r="C80" s="219"/>
-      <c r="D80" s="219"/>
-      <c r="E80" s="219"/>
-      <c r="F80" s="219"/>
-      <c r="G80" s="220"/>
-      <c r="H80" s="133">
-        <f>H77+H79</f>
-        <v>7262751.169999999</v>
-      </c>
-      <c r="I80" s="128"/>
-      <c r="J80" s="228"/>
-      <c r="K80" s="228"/>
-    </row>
-    <row r="81" spans="1:11" ht="18">
-      <c r="A81" s="218" t="s">
-        <v>95</v>
-      </c>
-      <c r="B81" s="219"/>
-      <c r="C81" s="219"/>
-      <c r="D81" s="219"/>
-      <c r="E81" s="219"/>
-      <c r="F81" s="219"/>
-      <c r="G81" s="220"/>
-      <c r="H81" s="134">
-        <f>H78+H76</f>
-        <v>0</v>
-      </c>
-      <c r="J81" s="144"/>
-    </row>
-    <row r="82" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A82" s="221" t="s">
-        <v>85</v>
-      </c>
-      <c r="B82" s="222"/>
-      <c r="C82" s="222"/>
-      <c r="D82" s="222"/>
-      <c r="E82" s="222"/>
-      <c r="F82" s="222"/>
-      <c r="G82" s="222"/>
-      <c r="H82" s="135">
-        <f>H79+H76</f>
-        <v>7262751.169999999</v>
+      <c r="B81" s="210"/>
+      <c r="C81" s="210"/>
+      <c r="D81" s="210"/>
+      <c r="E81" s="210"/>
+      <c r="F81" s="210"/>
+      <c r="G81" s="210"/>
+      <c r="H81" s="135">
+        <f>H78+H75</f>
+        <v>4494890.1399999997</v>
+      </c>
+      <c r="J81" s="7"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75" hidden="1">
+      <c r="A82" s="196" t="s">
+        <v>17</v>
+      </c>
+      <c r="B82" s="197"/>
+      <c r="C82" s="197"/>
+      <c r="D82" s="197"/>
+      <c r="E82" s="197"/>
+      <c r="F82" s="197"/>
+      <c r="G82" s="197"/>
+      <c r="H82" s="136">
+        <f>H67</f>
+        <v>0</v>
       </c>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:11" ht="18" hidden="1">
-      <c r="A83" s="212" t="s">
-        <v>17</v>
-      </c>
-      <c r="B83" s="213"/>
-      <c r="C83" s="213"/>
-      <c r="D83" s="213"/>
-      <c r="E83" s="213"/>
-      <c r="F83" s="213"/>
-      <c r="G83" s="213"/>
-      <c r="H83" s="136">
-        <f>H68</f>
-        <v>0</v>
-      </c>
+    <row r="83" spans="1:11" ht="18.75" hidden="1">
+      <c r="A83" s="137"/>
+      <c r="B83" s="137"/>
+      <c r="C83" s="137"/>
+      <c r="D83" s="137"/>
+      <c r="E83" s="137"/>
+      <c r="F83" s="137"/>
+      <c r="G83" s="137"/>
+      <c r="H83" s="138"/>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:11" ht="18" hidden="1">
+    <row r="84" spans="1:11" ht="18.75" hidden="1">
       <c r="A84" s="137"/>
       <c r="B84" s="137"/>
       <c r="C84" s="137"/>
@@ -3364,7 +3339,7 @@
       <c r="H84" s="138"/>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:11" ht="18" hidden="1">
+    <row r="85" spans="1:11" ht="18.75" hidden="1">
       <c r="A85" s="137"/>
       <c r="B85" s="137"/>
       <c r="C85" s="137"/>
@@ -3375,71 +3350,75 @@
       <c r="H85" s="138"/>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:11" ht="18" hidden="1">
-      <c r="A86" s="137"/>
-      <c r="B86" s="137"/>
-      <c r="C86" s="137"/>
-      <c r="D86" s="137"/>
-      <c r="E86" s="137"/>
-      <c r="F86" s="137"/>
-      <c r="G86" s="137"/>
-      <c r="H86" s="138"/>
-      <c r="J86" s="7"/>
-    </row>
-    <row r="87" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A87" s="139"/>
-      <c r="B87" s="139"/>
-      <c r="C87" s="139"/>
-      <c r="D87" s="139"/>
-      <c r="E87" s="139"/>
-      <c r="F87" s="139"/>
-      <c r="G87" s="139"/>
-      <c r="H87" s="139"/>
-    </row>
-    <row r="88" spans="1:11" ht="18">
-      <c r="A88" s="232" t="s">
+    <row r="86" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A86" s="139"/>
+      <c r="B86" s="139"/>
+      <c r="C86" s="139"/>
+      <c r="D86" s="139"/>
+      <c r="E86" s="139"/>
+      <c r="F86" s="139"/>
+      <c r="G86" s="139"/>
+      <c r="H86" s="139"/>
+    </row>
+    <row r="87" spans="1:11" ht="18.75">
+      <c r="A87" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="B88" s="233"/>
-      <c r="C88" s="233"/>
-      <c r="D88" s="233"/>
-      <c r="E88" s="233"/>
-      <c r="F88" s="233"/>
-      <c r="G88" s="233"/>
-      <c r="H88" s="234"/>
-    </row>
-    <row r="89" spans="1:11" ht="18">
-      <c r="A89" s="140" t="s">
+      <c r="B87" s="192"/>
+      <c r="C87" s="192"/>
+      <c r="D87" s="192"/>
+      <c r="E87" s="192"/>
+      <c r="F87" s="192"/>
+      <c r="G87" s="192"/>
+      <c r="H87" s="193"/>
+    </row>
+    <row r="88" spans="1:11" ht="18.75">
+      <c r="A88" s="140" t="s">
         <v>12</v>
       </c>
-      <c r="B89" s="141"/>
-      <c r="C89" s="141"/>
-      <c r="D89" s="141"/>
-      <c r="E89" s="141"/>
-      <c r="F89" s="141"/>
-      <c r="G89" s="141"/>
-      <c r="H89" s="142">
-        <v>2124228.4099193653</v>
+      <c r="B88" s="141"/>
+      <c r="C88" s="141"/>
+      <c r="D88" s="141"/>
+      <c r="E88" s="141"/>
+      <c r="F88" s="141"/>
+      <c r="G88" s="141"/>
+      <c r="H88" s="142">
+        <v>4176361.2016003644</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="81" t="s">
+        <v>129</v>
+      </c>
+      <c r="B89" s="82"/>
+      <c r="C89" s="82"/>
+      <c r="D89" s="82"/>
+      <c r="E89" s="82"/>
+      <c r="F89" s="82"/>
+      <c r="G89" s="82"/>
+      <c r="H89" s="143">
+        <f>Planilla!G32</f>
+        <v>3671141.4911220977</v>
       </c>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="81" t="s">
-        <v>130</v>
-      </c>
-      <c r="B90" s="82"/>
-      <c r="C90" s="82"/>
-      <c r="D90" s="82"/>
-      <c r="E90" s="82"/>
-      <c r="F90" s="82"/>
-      <c r="G90" s="82"/>
-      <c r="H90" s="143">
-        <f>Planilla!G32</f>
-        <v>4234282.671680999</v>
+      <c r="A90" s="78" t="s">
+        <v>157</v>
+      </c>
+      <c r="B90" s="79"/>
+      <c r="C90" s="79"/>
+      <c r="D90" s="79"/>
+      <c r="E90" s="79"/>
+      <c r="F90" s="79"/>
+      <c r="G90" s="79"/>
+      <c r="H90" s="183">
+        <f>-(H81)</f>
+        <v>-4494890.1399999997</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="78" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="B91" s="79"/>
       <c r="C91" s="79"/>
@@ -3447,264 +3426,216 @@
       <c r="E91" s="79"/>
       <c r="F91" s="79"/>
       <c r="G91" s="79"/>
-      <c r="H91" s="185">
-        <f>-(H82)</f>
-        <v>-7262751.169999999</v>
-      </c>
+      <c r="H91" s="183">
+        <f>-H68</f>
+        <v>0</v>
+      </c>
+      <c r="K91" s="6"/>
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="78" t="s">
-        <v>86</v>
-      </c>
-      <c r="B92" s="79"/>
+        <v>72</v>
+      </c>
+      <c r="B92" s="79" t="s">
+        <v>114</v>
+      </c>
       <c r="C92" s="79"/>
       <c r="D92" s="79"/>
       <c r="E92" s="79"/>
       <c r="F92" s="79"/>
       <c r="G92" s="79"/>
-      <c r="H92" s="185">
-        <f>-H69</f>
-        <v>0</v>
-      </c>
-      <c r="K92" s="6"/>
+      <c r="H92" s="123">
+        <v>133680</v>
+      </c>
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="78" t="s">
-        <v>73</v>
-      </c>
-      <c r="B93" s="79" t="s">
-        <v>115</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="B93" s="79"/>
       <c r="C93" s="79"/>
       <c r="D93" s="79"/>
       <c r="E93" s="79"/>
       <c r="F93" s="79"/>
       <c r="G93" s="79"/>
       <c r="H93" s="123">
-        <v>133680</v>
-      </c>
+        <f>180000-H92</f>
+        <v>46320</v>
+      </c>
+      <c r="I93" s="144"/>
     </row>
     <row r="94" spans="1:11">
-      <c r="A94" s="78" t="s">
-        <v>72</v>
-      </c>
-      <c r="B94" s="79"/>
-      <c r="C94" s="79"/>
-      <c r="D94" s="79"/>
-      <c r="E94" s="79"/>
-      <c r="F94" s="79"/>
-      <c r="G94" s="79"/>
-      <c r="H94" s="123">
-        <f>177000-H93</f>
-        <v>43320</v>
-      </c>
-      <c r="I94" s="144"/>
-    </row>
-    <row r="95" spans="1:11" ht="34.5" customHeight="1">
-      <c r="A95" s="225" t="s">
-        <v>148</v>
-      </c>
-      <c r="B95" s="226"/>
-      <c r="C95" s="226"/>
-      <c r="D95" s="226"/>
-      <c r="E95" s="226"/>
-      <c r="F95" s="226"/>
-      <c r="G95" s="227"/>
-      <c r="H95" s="123">
-        <f>-H96</f>
-        <v>1006446</v>
-      </c>
-      <c r="I95" s="144"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="78" t="s">
-        <v>146</v>
-      </c>
-      <c r="B96" s="79"/>
-      <c r="C96" s="79"/>
-      <c r="D96" s="79"/>
-      <c r="E96" s="79"/>
-      <c r="F96" s="79"/>
-      <c r="G96" s="79"/>
-      <c r="H96" s="184">
-        <f>-(1437.78*700)</f>
-        <v>-1006446</v>
-      </c>
-      <c r="I96" s="144"/>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="12" t="s">
+      <c r="A94" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B94" s="83"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="4"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="98"/>
+    </row>
+    <row r="95" spans="1:11" ht="18.75">
+      <c r="A95" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B95" s="23"/>
+      <c r="C95" s="23"/>
+      <c r="D95" s="23"/>
+      <c r="E95" s="23"/>
+      <c r="F95" s="23"/>
+      <c r="G95" s="23"/>
+      <c r="H95" s="84">
+        <f>SUM(H88:H94)</f>
+        <v>3532612.5527224625</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="97" spans="1:8" ht="16.5" thickBot="1">
+      <c r="A97" s="188" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" s="189"/>
+      <c r="C97" s="189"/>
+      <c r="D97" s="189"/>
+      <c r="E97" s="189"/>
+      <c r="F97" s="189"/>
+      <c r="G97" s="189"/>
+      <c r="H97" s="190"/>
+    </row>
+    <row r="98" spans="1:8" ht="15.75">
+      <c r="A98" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" s="87"/>
+      <c r="C98" s="87"/>
+      <c r="D98" s="87"/>
+      <c r="E98" s="87"/>
+      <c r="F98" s="87"/>
+      <c r="G98" s="87"/>
+      <c r="H98" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="61" t="s">
         <v>121</v>
       </c>
-      <c r="B97" s="83"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="98"/>
-    </row>
-    <row r="98" spans="1:8" ht="18">
-      <c r="A98" s="22" t="s">
+      <c r="B99" s="91"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="61"/>
+      <c r="E99" s="61"/>
+      <c r="F99" s="61"/>
+      <c r="G99" s="61"/>
+      <c r="H99" s="127"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="61"/>
+      <c r="B100" s="97"/>
+      <c r="C100" s="61"/>
+      <c r="D100" s="61"/>
+      <c r="E100" s="61"/>
+      <c r="F100" s="61"/>
+      <c r="G100" s="61"/>
+      <c r="H100" s="21"/>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" s="61"/>
+      <c r="B101" s="61"/>
+      <c r="C101" s="61"/>
+      <c r="D101" s="61"/>
+      <c r="E101" s="61"/>
+      <c r="F101" s="61"/>
+      <c r="G101" s="61"/>
+      <c r="H101" s="21"/>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B98" s="23"/>
-      <c r="C98" s="23"/>
-      <c r="D98" s="23"/>
-      <c r="E98" s="23"/>
-      <c r="F98" s="23"/>
-      <c r="G98" s="23"/>
-      <c r="H98" s="84">
-        <f>SUM(H89:H97)</f>
-        <v>-727240.0883996347</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" ht="15" thickBot="1"/>
-    <row r="100" spans="1:8" ht="16.2" thickBot="1">
-      <c r="A100" s="229" t="s">
-        <v>99</v>
-      </c>
-      <c r="B100" s="230"/>
-      <c r="C100" s="230"/>
-      <c r="D100" s="230"/>
-      <c r="E100" s="230"/>
-      <c r="F100" s="230"/>
-      <c r="G100" s="230"/>
-      <c r="H100" s="231"/>
-    </row>
-    <row r="101" spans="1:8" ht="15.6">
-      <c r="A101" s="87" t="s">
-        <v>12</v>
-      </c>
-      <c r="B101" s="87"/>
-      <c r="C101" s="87"/>
-      <c r="D101" s="87"/>
-      <c r="E101" s="87"/>
-      <c r="F101" s="87"/>
-      <c r="G101" s="87"/>
-      <c r="H101" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
-      <c r="A102" s="61" t="s">
-        <v>122</v>
-      </c>
-      <c r="B102" s="91"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="61"/>
-      <c r="E102" s="61"/>
-      <c r="F102" s="61"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="127"/>
-    </row>
-    <row r="103" spans="1:8">
-      <c r="A103" s="61"/>
-      <c r="B103" s="97"/>
-      <c r="C103" s="61"/>
-      <c r="D103" s="61"/>
-      <c r="E103" s="61"/>
-      <c r="F103" s="61"/>
-      <c r="G103" s="61"/>
-      <c r="H103" s="21"/>
-    </row>
-    <row r="104" spans="1:8">
-      <c r="A104" s="61"/>
-      <c r="B104" s="61"/>
-      <c r="C104" s="61"/>
-      <c r="D104" s="61"/>
-      <c r="E104" s="61"/>
-      <c r="F104" s="61"/>
-      <c r="G104" s="61"/>
-      <c r="H104" s="21"/>
-    </row>
-    <row r="105" spans="1:8">
-      <c r="A105" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="B105" s="85"/>
-      <c r="C105" s="85"/>
-      <c r="D105" s="85"/>
-      <c r="E105" s="85"/>
-      <c r="F105" s="85"/>
-      <c r="G105" s="85"/>
-      <c r="H105" s="86">
-        <f>SUM(H101:H104)</f>
-        <v>0</v>
-      </c>
+      <c r="B102" s="85"/>
+      <c r="C102" s="85"/>
+      <c r="D102" s="85"/>
+      <c r="E102" s="85"/>
+      <c r="F102" s="85"/>
+      <c r="G102" s="85"/>
+      <c r="H102" s="86">
+        <f>SUM(H98:H101)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" hidden="1">
+      <c r="A105" s="187"/>
+      <c r="B105" s="187"/>
+      <c r="C105" s="187"/>
+      <c r="D105" s="187"/>
+      <c r="E105" s="187"/>
+      <c r="F105" s="187"/>
+      <c r="G105" s="187"/>
+      <c r="H105" s="187"/>
+    </row>
+    <row r="106" spans="1:8" hidden="1">
+      <c r="A106" s="187"/>
+      <c r="B106" s="187"/>
+      <c r="C106" s="187"/>
+      <c r="D106" s="187"/>
+      <c r="E106" s="187"/>
+      <c r="F106" s="187"/>
+      <c r="G106" s="187"/>
+      <c r="H106" s="187"/>
+    </row>
+    <row r="107" spans="1:8" hidden="1">
+      <c r="A107" s="187"/>
+      <c r="B107" s="187"/>
+      <c r="C107" s="187"/>
+      <c r="D107" s="187"/>
+      <c r="E107" s="187"/>
+      <c r="F107" s="187"/>
+      <c r="G107" s="187"/>
+      <c r="H107" s="187"/>
     </row>
     <row r="108" spans="1:8" hidden="1">
-      <c r="A108" s="206"/>
-      <c r="B108" s="206"/>
-      <c r="C108" s="206"/>
-      <c r="D108" s="206"/>
-      <c r="E108" s="206"/>
-      <c r="F108" s="206"/>
-      <c r="G108" s="206"/>
-      <c r="H108" s="206"/>
-    </row>
-    <row r="109" spans="1:8" hidden="1">
-      <c r="A109" s="206"/>
-      <c r="B109" s="206"/>
-      <c r="C109" s="206"/>
-      <c r="D109" s="206"/>
-      <c r="E109" s="206"/>
-      <c r="F109" s="206"/>
-      <c r="G109" s="206"/>
-      <c r="H109" s="206"/>
-    </row>
-    <row r="110" spans="1:8" hidden="1">
-      <c r="A110" s="206"/>
-      <c r="B110" s="206"/>
-      <c r="C110" s="206"/>
-      <c r="D110" s="206"/>
-      <c r="E110" s="206"/>
-      <c r="F110" s="206"/>
-      <c r="G110" s="206"/>
-      <c r="H110" s="206"/>
-    </row>
-    <row r="111" spans="1:8" hidden="1">
-      <c r="A111" s="206"/>
-      <c r="B111" s="206"/>
-      <c r="C111" s="206"/>
-      <c r="D111" s="206"/>
-      <c r="E111" s="206"/>
-      <c r="F111" s="206"/>
-      <c r="G111" s="206"/>
-      <c r="H111" s="206"/>
+      <c r="A108" s="187"/>
+      <c r="B108" s="187"/>
+      <c r="C108" s="187"/>
+      <c r="D108" s="187"/>
+      <c r="E108" s="187"/>
+      <c r="F108" s="187"/>
+      <c r="G108" s="187"/>
+      <c r="H108" s="187"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A95:G95"/>
-    <mergeCell ref="J80:K80"/>
-    <mergeCell ref="A108:H111"/>
-    <mergeCell ref="A100:H100"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A83:G83"/>
+  <mergeCells count="29">
+    <mergeCell ref="A69:H70"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A82:G82"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A80:G80"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A81:G81"/>
-    <mergeCell ref="A77:G77"/>
-    <mergeCell ref="A80:G80"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A70:H71"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="J79:K79"/>
+    <mergeCell ref="A105:H108"/>
+    <mergeCell ref="A97:H97"/>
+    <mergeCell ref="A87:H87"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3715,23 +3646,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.44140625" customWidth="1"/>
-    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" customWidth="1"/>
     <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3740,7 +3671,7 @@
       <c r="C1" s="103"/>
       <c r="D1" s="103"/>
       <c r="E1" s="104" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1" s="105" t="str">
         <f>RESUMEN!F8</f>
@@ -3780,7 +3711,7 @@
       <c r="A3" s="115"/>
       <c r="B3" s="116"/>
       <c r="C3" s="101">
-        <v>2355849.88</v>
+        <v>2782455.8899999997</v>
       </c>
       <c r="D3" s="61"/>
       <c r="E3" s="61"/>
@@ -3791,7 +3722,7 @@
       <c r="J3" s="117"/>
       <c r="K3" s="117"/>
       <c r="L3" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M3" s="61"/>
       <c r="N3" s="61"/>
@@ -3799,12 +3730,12 @@
     <row r="4" spans="1:17" ht="18.75" customHeight="1">
       <c r="A4" s="118"/>
       <c r="B4" s="119" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C4" s="61"/>
       <c r="D4" s="61"/>
       <c r="E4" s="119" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F4" s="122"/>
       <c r="G4" s="117"/>
@@ -3813,18 +3744,18 @@
       <c r="J4" s="117"/>
       <c r="K4" s="117"/>
       <c r="L4" s="61" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M4" s="61"/>
       <c r="N4" s="61"/>
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="236">
+      <c r="B5" s="229">
         <f>C3</f>
-        <v>2355849.88</v>
-      </c>
-      <c r="C5" s="236"/>
+        <v>2782455.8899999997</v>
+      </c>
+      <c r="C5" s="229"/>
       <c r="D5" s="21"/>
       <c r="E5" s="121">
         <v>70000</v>
@@ -3841,10 +3772,10 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="238" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="239"/>
+      <c r="B6" s="231" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="232"/>
       <c r="D6" s="21"/>
       <c r="E6" s="119"/>
       <c r="F6" s="114"/>
@@ -3859,10 +3790,10 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="236">
+      <c r="B7" s="229">
         <v>2000000</v>
       </c>
-      <c r="C7" s="236"/>
+      <c r="C7" s="229"/>
       <c r="D7" s="21"/>
       <c r="E7" s="21"/>
       <c r="F7" s="114"/>
@@ -3886,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E8" s="109" t="s">
         <v>2</v>
@@ -3895,25 +3826,25 @@
         <v>16</v>
       </c>
       <c r="G8" s="112" t="s">
+        <v>166</v>
+      </c>
+      <c r="H8" s="112" t="s">
         <v>63</v>
       </c>
-      <c r="H8" s="112" t="s">
+      <c r="I8" s="112" t="s">
+        <v>137</v>
+      </c>
+      <c r="J8" s="112" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="112" t="s">
-        <v>138</v>
-      </c>
-      <c r="J8" s="112" t="s">
-        <v>65</v>
-      </c>
       <c r="K8" s="125" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L8" s="109" t="s">
         <v>7</v>
       </c>
       <c r="M8" s="109" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="N8" s="113" t="s">
         <v>8</v>
@@ -3930,17 +3861,17 @@
         <v>19</v>
       </c>
       <c r="D9" s="168" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E9" s="169">
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>209212.85961000001</v>
+        <v>176411.92014</v>
       </c>
       <c r="G9" s="180">
         <f>F9</f>
-        <v>209212.85961000001</v>
+        <v>176411.92014</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
@@ -3960,7 +3891,7 @@
       </c>
       <c r="L9" s="170">
         <f>B$5*E9</f>
-        <v>95411.920140000002</v>
+        <v>112689.46354499999</v>
       </c>
       <c r="M9" s="170">
         <f>B$7*E9</f>
@@ -3968,7 +3899,7 @@
       </c>
       <c r="N9" s="170">
         <f>H9+I9-J9+K9+L9+M9</f>
-        <v>176411.92014</v>
+        <v>193689.46354500001</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3986,11 +3917,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>334740.57537600002</v>
-      </c>
-      <c r="G10" s="181">
+        <v>282259.072224</v>
+      </c>
+      <c r="G10" s="180">
         <f>F10</f>
-        <v>334740.57537600002</v>
+        <v>282259.072224</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -4010,7 +3941,7 @@
       </c>
       <c r="L10" s="25">
         <f t="shared" ref="L10:L31" si="3">B$5*E10</f>
-        <v>152659.07222399997</v>
+        <v>180303.14167199997</v>
       </c>
       <c r="M10" s="25">
         <f t="shared" ref="M10:M31" si="4">B$7*E10</f>
@@ -4018,7 +3949,7 @@
       </c>
       <c r="N10" s="25">
         <f t="shared" ref="N10:N31" si="5">H10+I10-J10+K10+L10+M10</f>
-        <v>282259.072224</v>
+        <v>309903.14167199994</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
@@ -4032,17 +3963,17 @@
         <v>21</v>
       </c>
       <c r="D11" s="168" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" s="169">
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>248982.69334399997</v>
-      </c>
-      <c r="G11" s="181">
+        <v>209951.96421599999</v>
+      </c>
+      <c r="G11" s="180">
         <f>F11</f>
-        <v>248982.69334399997</v>
+        <v>209951.96421599999</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -4062,7 +3993,7 @@
       </c>
       <c r="L11" s="170">
         <f t="shared" si="3"/>
-        <v>113551.96421599999</v>
+        <v>134114.37389799999</v>
       </c>
       <c r="M11" s="170">
         <f t="shared" si="4"/>
@@ -4070,7 +4001,7 @@
       </c>
       <c r="N11" s="170">
         <f>H11+I11-J11+K11+L11+M11+E7</f>
-        <v>209951.96421599999</v>
+        <v>230514.37389799999</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
@@ -4081,25 +4012,25 @@
         <v>43</v>
       </c>
       <c r="C12" s="155" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D12" s="155" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E12" s="156">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="149">
-        <v>2977313.1195132579</v>
-      </c>
-      <c r="G12" s="182"/>
+        <v>3320511.6735152486</v>
+      </c>
+      <c r="G12" s="181"/>
       <c r="H12" s="150">
         <f t="shared" si="0"/>
-        <v>2977313.1195132579</v>
+        <v>3320511.6735152486</v>
       </c>
       <c r="I12" s="150">
         <f t="shared" si="6"/>
-        <v>110160.58542199056</v>
+        <v>122858.93192006422</v>
       </c>
       <c r="J12" s="150">
         <f t="shared" si="1"/>
@@ -4111,7 +4042,7 @@
       </c>
       <c r="L12" s="151">
         <f t="shared" si="3"/>
-        <v>126037.96857999999</v>
+        <v>148861.39011499999</v>
       </c>
       <c r="M12" s="151">
         <f t="shared" si="4"/>
@@ -4119,7 +4050,7 @@
       </c>
       <c r="N12" s="151">
         <f t="shared" si="5"/>
-        <v>3320511.6735152486</v>
+        <v>3699231.9955503126</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -4137,11 +4068,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>198881.36037000001</v>
-      </c>
-      <c r="G13" s="181">
+        <v>167700.22038000001</v>
+      </c>
+      <c r="G13" s="180">
         <f>F13</f>
-        <v>198881.36037000001</v>
+        <v>167700.22038000001</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -4161,7 +4092,7 @@
       </c>
       <c r="L13" s="25">
         <f t="shared" si="3"/>
-        <v>90700.220379999999</v>
+        <v>107124.55176499998</v>
       </c>
       <c r="M13" s="25">
         <f t="shared" si="4"/>
@@ -4169,7 +4100,7 @@
       </c>
       <c r="N13" s="25">
         <f t="shared" si="5"/>
-        <v>167700.22038000001</v>
+        <v>184124.55176499998</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4183,17 +4114,17 @@
         <v>24</v>
       </c>
       <c r="D14" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" s="45">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>185450.41135800001</v>
-      </c>
-      <c r="G14" s="181">
+        <v>156375.01069199998</v>
+      </c>
+      <c r="G14" s="180">
         <f>F14</f>
-        <v>185450.41135800001</v>
+        <v>156375.01069199998</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -4213,7 +4144,7 @@
       </c>
       <c r="L14" s="25">
         <f t="shared" si="3"/>
-        <v>84575.010691999996</v>
+        <v>99890.166450999997</v>
       </c>
       <c r="M14" s="25">
         <f t="shared" si="4"/>
@@ -4221,10 +4152,10 @@
       </c>
       <c r="N14" s="25">
         <f t="shared" si="5"/>
-        <v>156375.01069199998</v>
+        <v>171690.166451</v>
       </c>
       <c r="P14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4235,20 +4166,20 @@
         <v>46</v>
       </c>
       <c r="C15" s="93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D15" s="92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E15" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>213862.03426799999</v>
-      </c>
-      <c r="G15" s="181">
+        <v>97532.185031999994</v>
+      </c>
+      <c r="G15" s="180">
         <f>F15</f>
-        <v>213862.03426799999</v>
+        <v>97532.185031999994</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -4268,20 +4199,20 @@
       </c>
       <c r="L15" s="25">
         <f t="shared" si="3"/>
-        <v>97532.185031999994</v>
+        <v>115193.67384599999</v>
       </c>
       <c r="M15" s="25">
         <v>0</v>
       </c>
       <c r="N15" s="25">
         <f t="shared" si="5"/>
-        <v>97532.185031999994</v>
-      </c>
-      <c r="P15" s="186">
+        <v>115193.67384599999</v>
+      </c>
+      <c r="P15" s="184">
         <v>1006446</v>
       </c>
       <c r="Q15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1">
@@ -4292,20 +4223,20 @@
         <v>47</v>
       </c>
       <c r="C16" s="93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" s="45">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>276367.60467000003</v>
-      </c>
-      <c r="G16" s="181">
+        <v>233037.96857999999</v>
+      </c>
+      <c r="G16" s="180">
         <f>F16</f>
-        <v>276367.60467000003</v>
+        <v>233037.96857999999</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -4325,7 +4256,7 @@
       </c>
       <c r="L16" s="25">
         <f t="shared" si="3"/>
-        <v>126037.96857999999</v>
+        <v>148861.39011499999</v>
       </c>
       <c r="M16" s="25">
         <f t="shared" si="4"/>
@@ -4333,13 +4264,13 @@
       </c>
       <c r="N16" s="25">
         <f t="shared" si="5"/>
-        <v>233037.96857999999</v>
-      </c>
-      <c r="P16" s="186">
+        <v>255861.39011499999</v>
+      </c>
+      <c r="P16" s="184">
         <v>-82700</v>
       </c>
       <c r="Q16" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15" customHeight="1">
@@ -4353,17 +4284,17 @@
         <v>26</v>
       </c>
       <c r="D17" s="92" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E17" s="45">
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>198857.36037000001</v>
-      </c>
-      <c r="G17" s="181">
+        <v>167700.22038000001</v>
+      </c>
+      <c r="G17" s="180">
         <f>F17</f>
-        <v>198857.36037000001</v>
+        <v>167700.22038000001</v>
       </c>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
@@ -4383,7 +4314,7 @@
       </c>
       <c r="L17" s="25">
         <f t="shared" si="3"/>
-        <v>90700.220379999999</v>
+        <v>107124.55176499998</v>
       </c>
       <c r="M17" s="25">
         <f t="shared" si="4"/>
@@ -4391,9 +4322,9 @@
       </c>
       <c r="N17" s="25">
         <f t="shared" si="5"/>
-        <v>167700.22038000001</v>
-      </c>
-      <c r="P17" s="186"/>
+        <v>184124.55176499998</v>
+      </c>
+      <c r="P17" s="184"/>
     </row>
     <row r="18" spans="1:17" ht="15" customHeight="1">
       <c r="A18" s="166">
@@ -4410,19 +4341,19 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>346167.6955523981</v>
-      </c>
-      <c r="G18" s="181">
-        <f>RESUMEN!H54+RESUMEN!H44+RESUMEN!H40</f>
+        <v>326928.01097983681</v>
+      </c>
+      <c r="G18" s="180">
+        <f>RESUMEN!H44+RESUMEN!H40+RESUMEN!H53</f>
         <v>185000</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
-        <v>161167.6955523981</v>
+        <v>141928.01097983681</v>
       </c>
       <c r="I18" s="68">
         <f t="shared" si="6"/>
-        <v>5963.2047354387305</v>
+        <v>5251.3364062539622</v>
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
@@ -4434,7 +4365,7 @@
       </c>
       <c r="L18" s="170">
         <f t="shared" si="3"/>
-        <v>84575.010691999996</v>
+        <v>99890.166450999997</v>
       </c>
       <c r="M18" s="170">
         <f t="shared" si="4"/>
@@ -4442,9 +4373,9 @@
       </c>
       <c r="N18" s="170">
         <f t="shared" si="5"/>
-        <v>323505.91097983683</v>
-      </c>
-      <c r="P18" s="186"/>
+        <v>318869.51383709081</v>
+      </c>
+      <c r="P18" s="184"/>
     </row>
     <row r="19" spans="1:17" ht="15" customHeight="1">
       <c r="A19" s="145">
@@ -4457,22 +4388,22 @@
         <v>28</v>
       </c>
       <c r="D19" s="155" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E19" s="156">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="149">
-        <v>2022587.9576823395</v>
-      </c>
-      <c r="G19" s="182"/>
+        <v>2277755.8971485859</v>
+      </c>
+      <c r="G19" s="181"/>
       <c r="H19" s="150">
         <f t="shared" si="0"/>
-        <v>2022587.9576823395</v>
+        <v>2277755.8971485859</v>
       </c>
       <c r="I19" s="150">
         <f t="shared" si="6"/>
-        <v>74835.75443424657</v>
+        <v>84276.968194497691</v>
       </c>
       <c r="J19" s="150">
         <f t="shared" si="1"/>
@@ -4484,7 +4415,7 @@
       </c>
       <c r="L19" s="151">
         <f t="shared" si="3"/>
-        <v>97532.185031999994</v>
+        <v>115193.67384599999</v>
       </c>
       <c r="M19" s="151">
         <f t="shared" si="4"/>
@@ -4492,9 +4423,9 @@
       </c>
       <c r="N19" s="151">
         <f t="shared" si="5"/>
-        <v>2277755.8971485859</v>
-      </c>
-      <c r="P19" s="186"/>
+        <v>2560026.5391890835</v>
+      </c>
+      <c r="P19" s="184"/>
     </row>
     <row r="20" spans="1:17" ht="15" customHeight="1">
       <c r="A20" s="51">
@@ -4504,20 +4435,20 @@
         <v>51</v>
       </c>
       <c r="C20" s="100" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D20" s="96" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E20" s="46">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>276323.73069500003</v>
-      </c>
-      <c r="G20" s="181">
+        <v>233037.96857999999</v>
+      </c>
+      <c r="G20" s="180">
         <f>F20</f>
-        <v>276323.73069500003</v>
+        <v>233037.96857999999</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -4537,7 +4468,7 @@
       </c>
       <c r="L20" s="25">
         <f t="shared" si="3"/>
-        <v>126037.96857999999</v>
+        <v>148861.39011499999</v>
       </c>
       <c r="M20" s="25">
         <f t="shared" si="4"/>
@@ -4545,9 +4476,9 @@
       </c>
       <c r="N20" s="25">
         <f t="shared" si="5"/>
-        <v>233037.96857999999</v>
-      </c>
-      <c r="P20" s="186"/>
+        <v>255861.39011499999</v>
+      </c>
+      <c r="P20" s="184"/>
     </row>
     <row r="21" spans="1:17" ht="15" customHeight="1">
       <c r="A21" s="145">
@@ -4560,24 +4491,24 @@
         <v>30</v>
       </c>
       <c r="D21" s="153" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E21" s="154">
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="149">
-        <v>955380.93852864171</v>
-      </c>
-      <c r="G21" s="183">
-        <v>120000</v>
+        <v>1033990.2536342014</v>
+      </c>
+      <c r="G21" s="182">
+        <v>90700.72</v>
       </c>
       <c r="H21" s="150">
         <f t="shared" si="0"/>
-        <v>835380.93852864171</v>
+        <v>943289.53363420139</v>
       </c>
       <c r="I21" s="150">
         <f t="shared" si="6"/>
-        <v>30909.094725559746</v>
+        <v>34901.712744465454</v>
       </c>
       <c r="J21" s="150">
         <f t="shared" si="1"/>
@@ -4589,7 +4520,7 @@
       </c>
       <c r="L21" s="151">
         <f t="shared" si="3"/>
-        <v>90700.220379999999</v>
+        <v>107124.55176499998</v>
       </c>
       <c r="M21" s="151">
         <f t="shared" si="4"/>
@@ -4597,9 +4528,9 @@
       </c>
       <c r="N21" s="151">
         <f t="shared" si="5"/>
-        <v>1033990.2536342014</v>
-      </c>
-      <c r="P21" s="186"/>
+        <v>1162315.7981436667</v>
+      </c>
+      <c r="P21" s="184"/>
     </row>
     <row r="22" spans="1:17" ht="15" customHeight="1">
       <c r="A22" s="51">
@@ -4612,17 +4543,17 @@
         <v>31</v>
       </c>
       <c r="D22" s="93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E22" s="47">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>185450.41135800001</v>
-      </c>
-      <c r="G22" s="181">
+        <v>156375.01069199998</v>
+      </c>
+      <c r="G22" s="180">
         <f>F22</f>
-        <v>185450.41135800001</v>
+        <v>156375.01069199998</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -4642,7 +4573,7 @@
       </c>
       <c r="L22" s="25">
         <f t="shared" si="3"/>
-        <v>84575.010691999996</v>
+        <v>99890.166450999997</v>
       </c>
       <c r="M22" s="25">
         <f t="shared" si="4"/>
@@ -4650,9 +4581,9 @@
       </c>
       <c r="N22" s="25">
         <f t="shared" si="5"/>
-        <v>156375.01069199998</v>
-      </c>
-      <c r="P22" s="186"/>
+        <v>171690.166451</v>
+      </c>
+      <c r="P22" s="184"/>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1">
       <c r="A23" s="51">
@@ -4665,24 +4596,25 @@
         <v>32</v>
       </c>
       <c r="D23" s="94" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E23" s="48">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>217945.13197416998</v>
-      </c>
-      <c r="G23" s="181">
-        <v>128384.447868</v>
+        <v>273206.61445009825</v>
+      </c>
+      <c r="G23" s="180">
+        <f>F23</f>
+        <v>273206.61445009825</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
-        <v>89560.684106169982</v>
+        <v>0</v>
       </c>
       <c r="I23" s="24">
         <f t="shared" si="6"/>
-        <v>3313.74531192829</v>
+        <v>0</v>
       </c>
       <c r="J23" s="24">
         <f t="shared" si="1"/>
@@ -4694,7 +4626,7 @@
       </c>
       <c r="L23" s="25">
         <f t="shared" si="3"/>
-        <v>97532.185031999994</v>
+        <v>115193.67384599999</v>
       </c>
       <c r="M23" s="25">
         <f t="shared" si="4"/>
@@ -4702,9 +4634,9 @@
       </c>
       <c r="N23" s="25">
         <f t="shared" si="5"/>
-        <v>273206.61445009825</v>
-      </c>
-      <c r="P23" s="186"/>
+        <v>197993.67384599999</v>
+      </c>
+      <c r="P23" s="184"/>
     </row>
     <row r="24" spans="1:17" ht="15" customHeight="1">
       <c r="A24" s="51">
@@ -4721,11 +4653,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>276367.60467000003</v>
-      </c>
-      <c r="G24" s="181">
+        <v>233037.96857999999</v>
+      </c>
+      <c r="G24" s="180">
         <f>F24</f>
-        <v>276367.60467000003</v>
+        <v>233037.96857999999</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -4745,7 +4677,7 @@
       </c>
       <c r="L24" s="25">
         <f t="shared" si="3"/>
-        <v>126037.96857999999</v>
+        <v>148861.39011499999</v>
       </c>
       <c r="M24" s="25">
         <f t="shared" si="4"/>
@@ -4753,9 +4685,9 @@
       </c>
       <c r="N24" s="25">
         <f t="shared" si="5"/>
-        <v>233037.96857999999</v>
-      </c>
-      <c r="P24" s="186"/>
+        <v>255861.39011499999</v>
+      </c>
+      <c r="P24" s="184"/>
     </row>
     <row r="25" spans="1:17" s="1" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="51">
@@ -4765,20 +4697,20 @@
         <v>56</v>
       </c>
       <c r="C25" s="95" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" s="95" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E25" s="49">
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>198881.36037000001</v>
-      </c>
-      <c r="G25" s="181">
+        <v>167700.22038000001</v>
+      </c>
+      <c r="G25" s="180">
         <f>F25</f>
-        <v>198881.36037000001</v>
+        <v>167700.22038000001</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -4798,7 +4730,7 @@
       </c>
       <c r="L25" s="25">
         <f t="shared" si="3"/>
-        <v>90700.220379999999</v>
+        <v>107124.55176499998</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="4"/>
@@ -4806,9 +4738,9 @@
       </c>
       <c r="N25" s="25">
         <f t="shared" si="5"/>
-        <v>167700.22038000001</v>
-      </c>
-      <c r="P25" s="187"/>
+        <v>184124.55176499998</v>
+      </c>
+      <c r="P25" s="185"/>
     </row>
     <row r="26" spans="1:17" ht="15" customHeight="1">
       <c r="A26" s="51">
@@ -4825,11 +4757,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>185450.41135800001</v>
-      </c>
-      <c r="G26" s="181">
+        <v>156375.01069199998</v>
+      </c>
+      <c r="G26" s="180">
         <f>F26</f>
-        <v>185450.41135800001</v>
+        <v>156375.01069199998</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -4849,7 +4781,7 @@
       </c>
       <c r="L26" s="25">
         <f t="shared" si="3"/>
-        <v>84575.010691999996</v>
+        <v>99890.166450999997</v>
       </c>
       <c r="M26" s="25">
         <f t="shared" si="4"/>
@@ -4857,9 +4789,9 @@
       </c>
       <c r="N26" s="25">
         <f t="shared" si="5"/>
-        <v>156375.01069199998</v>
-      </c>
-      <c r="P26" s="186"/>
+        <v>171690.166451</v>
+      </c>
+      <c r="P26" s="184"/>
     </row>
     <row r="27" spans="1:17" ht="15" customHeight="1">
       <c r="A27" s="145">
@@ -4872,24 +4804,24 @@
         <v>35</v>
       </c>
       <c r="D27" s="147" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E27" s="148">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="149">
-        <v>2863079.3289879635</v>
-      </c>
-      <c r="G27" s="182">
-        <v>213900</v>
+        <v>2927531.1491925181</v>
+      </c>
+      <c r="G27" s="181">
+        <v>180332</v>
       </c>
       <c r="H27" s="172">
         <f t="shared" si="0"/>
-        <v>2649179.3289879635</v>
+        <v>2747199.1491925181</v>
       </c>
       <c r="I27" s="150">
         <f t="shared" si="6"/>
-        <v>98019.63517255467</v>
+        <v>101646.36852012319</v>
       </c>
       <c r="J27" s="150">
         <f t="shared" si="1"/>
@@ -4901,7 +4833,7 @@
       </c>
       <c r="L27" s="151">
         <f t="shared" si="3"/>
-        <v>97532.185031999994</v>
+        <v>115193.67384599999</v>
       </c>
       <c r="M27" s="151">
         <f t="shared" si="4"/>
@@ -4909,7 +4841,11 @@
       </c>
       <c r="N27" s="151">
         <f t="shared" si="5"/>
-        <v>2927531.1491925181</v>
+        <v>3046839.1915586414</v>
+      </c>
+      <c r="O27" s="236">
+        <f>L27+M27</f>
+        <v>197993.67384599999</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="17.25" customHeight="1">
@@ -4927,16 +4863,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>1080904.8507179199</v>
-      </c>
-      <c r="G28" s="181"/>
+        <v>1353936.2987744827</v>
+      </c>
+      <c r="G28" s="180"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>1080904.8507179199</v>
+        <v>1353936.2987744827</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="6"/>
-        <v>39993.479476563043</v>
+        <v>50095.643054655869</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
@@ -4945,7 +4881,7 @@
       <c r="K28" s="24"/>
       <c r="L28" s="25">
         <f t="shared" si="3"/>
-        <v>126037.96857999999</v>
+        <v>148861.39011499999</v>
       </c>
       <c r="M28" s="25">
         <f t="shared" si="4"/>
@@ -4953,7 +4889,7 @@
       </c>
       <c r="N28" s="25">
         <f t="shared" si="5"/>
-        <v>1353936.2987744827</v>
+        <v>1659893.3319441385</v>
       </c>
       <c r="O28" s="7"/>
     </row>
@@ -4965,18 +4901,18 @@
         <v>60</v>
       </c>
       <c r="C29" s="95" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D29" s="95"/>
       <c r="E29" s="49">
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>198857.36037000001</v>
-      </c>
-      <c r="G29" s="181">
+        <v>167700.22038000001</v>
+      </c>
+      <c r="G29" s="180">
         <f>F29</f>
-        <v>198857.36037000001</v>
+        <v>167700.22038000001</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4996,7 +4932,7 @@
       </c>
       <c r="L29" s="25">
         <f t="shared" si="3"/>
-        <v>90700.220379999999</v>
+        <v>107124.55176499998</v>
       </c>
       <c r="M29" s="25">
         <f t="shared" si="4"/>
@@ -5004,7 +4940,7 @@
       </c>
       <c r="N29" s="25">
         <f t="shared" si="5"/>
-        <v>167700.22038000001</v>
+        <v>184124.55176499998</v>
       </c>
       <c r="O29" s="7"/>
       <c r="P29" s="7">
@@ -5012,7 +4948,7 @@
         <v>923746</v>
       </c>
       <c r="Q29" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1">
@@ -5023,20 +4959,20 @@
         <v>61</v>
       </c>
       <c r="C30" s="95" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D30" s="95" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E30" s="49">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>185450.41135800001</v>
-      </c>
-      <c r="G30" s="181">
+        <v>156375.01069199998</v>
+      </c>
+      <c r="G30" s="180">
         <f>F30</f>
-        <v>185450.41135800001</v>
+        <v>156375.01069199998</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -5056,7 +4992,7 @@
       </c>
       <c r="L30" s="25">
         <f t="shared" si="3"/>
-        <v>84575.010691999996</v>
+        <v>99890.166450999997</v>
       </c>
       <c r="M30" s="25">
         <f t="shared" si="4"/>
@@ -5064,7 +5000,7 @@
       </c>
       <c r="N30" s="25">
         <f t="shared" si="5"/>
-        <v>156375.01069199998</v>
+        <v>171690.166451</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="15" customHeight="1">
@@ -5082,11 +5018,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>213862.03426799999</v>
-      </c>
-      <c r="G31" s="181">
+        <v>180332.18503200001</v>
+      </c>
+      <c r="G31" s="180">
         <f>F31</f>
-        <v>213862.03426799999</v>
+        <v>180332.18503200001</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -5106,7 +5042,7 @@
       </c>
       <c r="L31" s="25">
         <f t="shared" si="3"/>
-        <v>97532.185031999994</v>
+        <v>115193.67384599999</v>
       </c>
       <c r="M31" s="25">
         <f t="shared" si="4"/>
@@ -5114,10 +5050,10 @@
       </c>
       <c r="N31" s="25">
         <f t="shared" si="5"/>
-        <v>180332.18503200001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="15.6">
+        <v>197993.67384599999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5131,19 +5067,19 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>14050377.246769693</v>
+        <v>14455762.054366976</v>
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)</f>
-        <v>4234282.671680999</v>
+        <v>3671141.4911220977</v>
       </c>
       <c r="H32" s="124">
         <f>SUM(H9:H31)</f>
-        <v>9816094.575088691</v>
+        <v>10784620.563244874</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>363195.49927828164</v>
+        <v>399030.96084006038</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="7">SUM(J9:J31)</f>
@@ -5155,7 +5091,7 @@
       </c>
       <c r="L32" s="54">
         <f>SUM(L9:L31)</f>
-        <v>2355849.88</v>
+        <v>2782455.8899999992</v>
       </c>
       <c r="M32" s="90">
         <f>SUM(M9:M31)</f>
@@ -5163,117 +5099,117 @@
       </c>
       <c r="N32" s="54">
         <f>SUM(N9:N31)</f>
-        <v>14452339.954366975</v>
+        <v>15883307.414084934</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:14" hidden="1">
-      <c r="B34" s="235"/>
-      <c r="C34" s="235"/>
-      <c r="D34" s="235"/>
-      <c r="E34" s="235"/>
-      <c r="F34" s="235"/>
-      <c r="G34" s="235"/>
-      <c r="H34" s="235"/>
-      <c r="I34" s="235"/>
-      <c r="J34" s="235"/>
-      <c r="K34" s="235"/>
-      <c r="L34" s="235"/>
-      <c r="M34" s="235"/>
-      <c r="N34" s="235"/>
+      <c r="B34" s="228"/>
+      <c r="C34" s="228"/>
+      <c r="D34" s="228"/>
+      <c r="E34" s="228"/>
+      <c r="F34" s="228"/>
+      <c r="G34" s="228"/>
+      <c r="H34" s="228"/>
+      <c r="I34" s="228"/>
+      <c r="J34" s="228"/>
+      <c r="K34" s="228"/>
+      <c r="L34" s="228"/>
+      <c r="M34" s="228"/>
+      <c r="N34" s="228"/>
     </row>
     <row r="35" spans="1:14" hidden="1">
-      <c r="B35" s="235"/>
-      <c r="C35" s="235"/>
-      <c r="D35" s="235"/>
-      <c r="E35" s="235"/>
-      <c r="F35" s="235"/>
-      <c r="G35" s="235"/>
-      <c r="H35" s="235"/>
-      <c r="I35" s="235"/>
-      <c r="J35" s="235"/>
-      <c r="K35" s="235"/>
-      <c r="L35" s="235"/>
-      <c r="M35" s="235"/>
-      <c r="N35" s="235"/>
+      <c r="B35" s="228"/>
+      <c r="C35" s="228"/>
+      <c r="D35" s="228"/>
+      <c r="E35" s="228"/>
+      <c r="F35" s="228"/>
+      <c r="G35" s="228"/>
+      <c r="H35" s="228"/>
+      <c r="I35" s="228"/>
+      <c r="J35" s="228"/>
+      <c r="K35" s="228"/>
+      <c r="L35" s="228"/>
+      <c r="M35" s="228"/>
+      <c r="N35" s="228"/>
     </row>
     <row r="36" spans="1:14" hidden="1">
-      <c r="B36" s="235"/>
-      <c r="C36" s="235"/>
-      <c r="D36" s="235"/>
-      <c r="E36" s="235"/>
-      <c r="F36" s="235"/>
-      <c r="G36" s="235"/>
-      <c r="H36" s="235"/>
-      <c r="I36" s="235"/>
-      <c r="J36" s="235"/>
-      <c r="K36" s="235"/>
-      <c r="L36" s="235"/>
-      <c r="M36" s="235"/>
-      <c r="N36" s="235"/>
+      <c r="B36" s="228"/>
+      <c r="C36" s="228"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="228"/>
+      <c r="F36" s="228"/>
+      <c r="G36" s="228"/>
+      <c r="H36" s="228"/>
+      <c r="I36" s="228"/>
+      <c r="J36" s="228"/>
+      <c r="K36" s="228"/>
+      <c r="L36" s="228"/>
+      <c r="M36" s="228"/>
+      <c r="N36" s="228"/>
     </row>
     <row r="37" spans="1:14" hidden="1">
-      <c r="B37" s="235"/>
-      <c r="C37" s="235"/>
-      <c r="D37" s="235"/>
-      <c r="E37" s="235"/>
-      <c r="F37" s="235"/>
-      <c r="G37" s="235"/>
-      <c r="H37" s="235"/>
-      <c r="I37" s="235"/>
-      <c r="J37" s="235"/>
-      <c r="K37" s="235"/>
-      <c r="L37" s="235"/>
-      <c r="M37" s="235"/>
-      <c r="N37" s="235"/>
+      <c r="B37" s="228"/>
+      <c r="C37" s="228"/>
+      <c r="D37" s="228"/>
+      <c r="E37" s="228"/>
+      <c r="F37" s="228"/>
+      <c r="G37" s="228"/>
+      <c r="H37" s="228"/>
+      <c r="I37" s="228"/>
+      <c r="J37" s="228"/>
+      <c r="K37" s="228"/>
+      <c r="L37" s="228"/>
+      <c r="M37" s="228"/>
+      <c r="N37" s="228"/>
     </row>
     <row r="38" spans="1:14" hidden="1">
-      <c r="A38" s="237"/>
-      <c r="B38" s="237"/>
-      <c r="C38" s="237"/>
-      <c r="D38" s="237"/>
-      <c r="E38" s="237"/>
-      <c r="F38" s="237"/>
-      <c r="G38" s="237"/>
-      <c r="H38" s="237"/>
-      <c r="I38" s="237"/>
-      <c r="J38" s="237"/>
-      <c r="K38" s="237"/>
-      <c r="L38" s="237"/>
-      <c r="M38" s="237"/>
-      <c r="N38" s="237"/>
+      <c r="A38" s="230"/>
+      <c r="B38" s="230"/>
+      <c r="C38" s="230"/>
+      <c r="D38" s="230"/>
+      <c r="E38" s="230"/>
+      <c r="F38" s="230"/>
+      <c r="G38" s="230"/>
+      <c r="H38" s="230"/>
+      <c r="I38" s="230"/>
+      <c r="J38" s="230"/>
+      <c r="K38" s="230"/>
+      <c r="L38" s="230"/>
+      <c r="M38" s="230"/>
+      <c r="N38" s="230"/>
     </row>
     <row r="39" spans="1:14" hidden="1">
-      <c r="A39" s="237"/>
-      <c r="B39" s="237"/>
-      <c r="C39" s="237"/>
-      <c r="D39" s="237"/>
-      <c r="E39" s="237"/>
-      <c r="F39" s="237"/>
-      <c r="G39" s="237"/>
-      <c r="H39" s="237"/>
-      <c r="I39" s="237"/>
-      <c r="J39" s="237"/>
-      <c r="K39" s="237"/>
-      <c r="L39" s="237"/>
-      <c r="M39" s="237"/>
-      <c r="N39" s="237"/>
+      <c r="A39" s="230"/>
+      <c r="B39" s="230"/>
+      <c r="C39" s="230"/>
+      <c r="D39" s="230"/>
+      <c r="E39" s="230"/>
+      <c r="F39" s="230"/>
+      <c r="G39" s="230"/>
+      <c r="H39" s="230"/>
+      <c r="I39" s="230"/>
+      <c r="J39" s="230"/>
+      <c r="K39" s="230"/>
+      <c r="L39" s="230"/>
+      <c r="M39" s="230"/>
+      <c r="N39" s="230"/>
     </row>
     <row r="40" spans="1:14" hidden="1">
-      <c r="A40" s="237"/>
-      <c r="B40" s="237"/>
-      <c r="C40" s="237"/>
-      <c r="D40" s="237"/>
-      <c r="E40" s="237"/>
-      <c r="F40" s="237"/>
-      <c r="G40" s="237"/>
-      <c r="H40" s="237"/>
-      <c r="I40" s="237"/>
-      <c r="J40" s="237"/>
-      <c r="K40" s="237"/>
-      <c r="L40" s="237"/>
-      <c r="M40" s="237"/>
-      <c r="N40" s="237"/>
+      <c r="A40" s="230"/>
+      <c r="B40" s="230"/>
+      <c r="C40" s="230"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="230"/>
+      <c r="H40" s="230"/>
+      <c r="I40" s="230"/>
+      <c r="J40" s="230"/>
+      <c r="K40" s="230"/>
+      <c r="L40" s="230"/>
+      <c r="M40" s="230"/>
+      <c r="N40" s="230"/>
     </row>
     <row r="41" spans="1:14">
       <c r="N41" s="7"/>
@@ -5295,25 +5231,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="240" t="s">
-        <v>92</v>
-      </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="242"/>
+      <c r="A1" s="233" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="235"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5322,7 +5258,7 @@
     <row r="3" spans="1:7">
       <c r="A3" s="57"/>
       <c r="B3" s="59" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G3" s="31"/>
     </row>
@@ -5349,13 +5285,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5372,7 +5308,7 @@
         <v>15</v>
       </c>
       <c r="F8" s="74" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G8" s="29" t="s">
         <v>8</v>
@@ -5397,7 +5333,7 @@
       </c>
       <c r="F9" s="70"/>
       <c r="G9" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5419,7 +5355,7 @@
       </c>
       <c r="F10" s="70"/>
       <c r="G10" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -5441,7 +5377,7 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5463,7 +5399,7 @@
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -5485,7 +5421,7 @@
       </c>
       <c r="F13" s="70"/>
       <c r="G13" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -5533,7 +5469,7 @@
       </c>
       <c r="F15" s="70"/>
       <c r="G15" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -5544,7 +5480,7 @@
         <v>47</v>
       </c>
       <c r="C16" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D16" s="45">
         <v>5.3499999999999999E-2</v>
@@ -5555,7 +5491,7 @@
       </c>
       <c r="F16" s="70"/>
       <c r="G16" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -5577,7 +5513,7 @@
       </c>
       <c r="F17" s="70"/>
       <c r="G17" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -5599,7 +5535,7 @@
       </c>
       <c r="F18" s="70"/>
       <c r="G18" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -5647,7 +5583,7 @@
       </c>
       <c r="F20" s="70"/>
       <c r="G20" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -5669,7 +5605,7 @@
       </c>
       <c r="F21" s="70"/>
       <c r="G21" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -5691,7 +5627,7 @@
       </c>
       <c r="F22" s="70"/>
       <c r="G22" s="70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -5713,10 +5649,10 @@
       </c>
       <c r="F23" s="70"/>
       <c r="G23" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5735,10 +5671,10 @@
       </c>
       <c r="F24" s="70"/>
       <c r="G24" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5746,7 +5682,7 @@
         <v>56</v>
       </c>
       <c r="C25" s="65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D25" s="49">
         <v>3.85E-2</v>
@@ -5757,10 +5693,10 @@
       </c>
       <c r="F25" s="70"/>
       <c r="G25" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5779,10 +5715,10 @@
       </c>
       <c r="F26" s="70"/>
       <c r="G26" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5808,7 +5744,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5827,10 +5763,10 @@
       </c>
       <c r="F28" s="70"/>
       <c r="G28" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5849,10 +5785,10 @@
       </c>
       <c r="F29" s="70"/>
       <c r="G29" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5871,10 +5807,10 @@
       </c>
       <c r="F30" s="70"/>
       <c r="G30" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5893,10 +5829,10 @@
       </c>
       <c r="F31" s="70"/>
       <c r="G31" s="70" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="15.6">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5916,7 +5852,7 @@
     </row>
     <row r="34" spans="3:5" ht="13.5" customHeight="1">
       <c r="C34" s="77" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D34" s="75"/>
       <c r="E34" s="76">
